--- a/listone.xlsx
+++ b/listone.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
   <si>
     <t>Quotazioni Fantacalcio Stagione 2026 27</t>
   </si>
@@ -1342,6 +1342,9 @@
     <t>Helgason</t>
   </si>
   <si>
+    <t>Cissè A.</t>
+  </si>
+  <si>
     <t>El Azzouzi O.</t>
   </si>
   <si>
@@ -1432,6 +1435,9 @@
     <t>Dagasso</t>
   </si>
   <si>
+    <t>Forson O.</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -1624,6 +1630,9 @@
     <t>Adorante</t>
   </si>
   <si>
+    <t>Milik</t>
+  </si>
+  <si>
     <t>Borrelli</t>
   </si>
   <si>
@@ -1700,6 +1709,9 @@
   </si>
   <si>
     <t>Lauberbach</t>
+  </si>
+  <si>
+    <t>Lontani</t>
   </si>
   <si>
     <t>Calciatori Ceduti 2026 27</t>
@@ -1811,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:M503"/>
+  <dimension ref="A1:M507"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5509,7 +5521,7 @@
         <v>132</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F91" s="0">
         <v>8</v>
@@ -17633,60 +17645,60 @@
     </row>
     <row r="387">
       <c r="A387" s="0">
-        <v>6225</v>
+        <v>6618</v>
       </c>
       <c r="B387" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>441</v>
       </c>
       <c r="E387" s="0" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F387" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G387" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H387" s="0">
         <v>0</v>
       </c>
       <c r="I387" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J387" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K387" s="0">
         <v>0</v>
       </c>
       <c r="L387" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M387" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0">
-        <v>6815</v>
+        <v>6225</v>
       </c>
       <c r="B388" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>442</v>
       </c>
       <c r="E388" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F388" s="0">
         <v>2</v>
@@ -17707,27 +17719,27 @@
         <v>0</v>
       </c>
       <c r="L388" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M388" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0">
-        <v>6903</v>
+        <v>6815</v>
       </c>
       <c r="B389" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>443</v>
       </c>
       <c r="E389" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F389" s="0">
         <v>2</v>
@@ -17748,21 +17760,21 @@
         <v>0</v>
       </c>
       <c r="L389" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M389" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0">
-        <v>6917</v>
+        <v>6903</v>
       </c>
       <c r="B390" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>444</v>
@@ -17789,27 +17801,27 @@
         <v>0</v>
       </c>
       <c r="L390" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M390" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0">
-        <v>6980</v>
+        <v>6917</v>
       </c>
       <c r="B391" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>445</v>
       </c>
       <c r="E391" s="0" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F391" s="0">
         <v>2</v>
@@ -17830,27 +17842,27 @@
         <v>0</v>
       </c>
       <c r="L391" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M391" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0">
-        <v>5457</v>
+        <v>6980</v>
       </c>
       <c r="B392" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>446</v>
       </c>
       <c r="E392" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F392" s="0">
         <v>2</v>
@@ -17871,7 +17883,7 @@
         <v>0</v>
       </c>
       <c r="L392" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M392" s="0">
         <v>5</v>
@@ -17879,19 +17891,19 @@
     </row>
     <row r="393">
       <c r="A393" s="0">
-        <v>5295</v>
+        <v>5457</v>
       </c>
       <c r="B393" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C393" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="D393" s="0" t="s">
         <v>447</v>
       </c>
-      <c r="D393" s="0" t="s">
-        <v>448</v>
-      </c>
       <c r="E393" s="0" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F393" s="0">
         <v>2</v>
@@ -17912,27 +17924,27 @@
         <v>0</v>
       </c>
       <c r="L393" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M393" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0">
-        <v>5880</v>
+        <v>5295</v>
       </c>
       <c r="B394" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>98</v>
+        <v>448</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>449</v>
       </c>
       <c r="E394" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F394" s="0">
         <v>2</v>
@@ -17961,19 +17973,19 @@
     </row>
     <row r="395">
       <c r="A395" s="0">
-        <v>7138</v>
+        <v>5880</v>
       </c>
       <c r="B395" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>291</v>
+        <v>98</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>450</v>
       </c>
       <c r="E395" s="0" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F395" s="0">
         <v>2</v>
@@ -17994,7 +18006,7 @@
         <v>0</v>
       </c>
       <c r="L395" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M395" s="0">
         <v>6</v>
@@ -18002,7 +18014,7 @@
     </row>
     <row r="396">
       <c r="A396" s="0">
-        <v>6219</v>
+        <v>7138</v>
       </c>
       <c r="B396" s="0" t="s">
         <v>286</v>
@@ -18014,7 +18026,7 @@
         <v>451</v>
       </c>
       <c r="E396" s="0" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F396" s="0">
         <v>2</v>
@@ -18038,12 +18050,12 @@
         <v>5</v>
       </c>
       <c r="M396" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0">
-        <v>6246</v>
+        <v>6219</v>
       </c>
       <c r="B397" s="0" t="s">
         <v>286</v>
@@ -18084,19 +18096,19 @@
     </row>
     <row r="398">
       <c r="A398" s="0">
-        <v>7418</v>
+        <v>6246</v>
       </c>
       <c r="B398" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>453</v>
       </c>
       <c r="E398" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F398" s="0">
         <v>2</v>
@@ -18117,27 +18129,27 @@
         <v>0</v>
       </c>
       <c r="L398" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M398" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0">
-        <v>526</v>
+        <v>7418</v>
       </c>
       <c r="B399" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>454</v>
       </c>
       <c r="E399" s="0" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F399" s="0">
         <v>2</v>
@@ -18158,68 +18170,68 @@
         <v>0</v>
       </c>
       <c r="L399" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M399" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0">
-        <v>7165</v>
+        <v>526</v>
       </c>
       <c r="B400" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>455</v>
       </c>
       <c r="E400" s="0" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F400" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G400" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H400" s="0">
         <v>0</v>
       </c>
       <c r="I400" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J400" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K400" s="0">
         <v>0</v>
       </c>
       <c r="L400" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M400" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0">
-        <v>7357</v>
+        <v>7165</v>
       </c>
       <c r="B401" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>456</v>
       </c>
       <c r="E401" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F401" s="0">
         <v>1</v>
@@ -18248,19 +18260,19 @@
     </row>
     <row r="402">
       <c r="A402" s="0">
-        <v>7456</v>
+        <v>7357</v>
       </c>
       <c r="B402" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>457</v>
       </c>
       <c r="E402" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F402" s="0">
         <v>1</v>
@@ -18281,21 +18293,21 @@
         <v>0</v>
       </c>
       <c r="L402" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M402" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0">
-        <v>5725</v>
+        <v>7456</v>
       </c>
       <c r="B403" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>458</v>
@@ -18330,19 +18342,19 @@
     </row>
     <row r="404">
       <c r="A404" s="0">
-        <v>6191</v>
+        <v>5725</v>
       </c>
       <c r="B404" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>459</v>
       </c>
       <c r="E404" s="0" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F404" s="0">
         <v>1</v>
@@ -18363,21 +18375,21 @@
         <v>0</v>
       </c>
       <c r="L404" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M404" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0">
-        <v>7345</v>
+        <v>6191</v>
       </c>
       <c r="B405" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>460</v>
@@ -18412,19 +18424,19 @@
     </row>
     <row r="406">
       <c r="A406" s="0">
-        <v>7248</v>
+        <v>7345</v>
       </c>
       <c r="B406" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>461</v>
       </c>
       <c r="E406" s="0" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F406" s="0">
         <v>1</v>
@@ -18445,15 +18457,15 @@
         <v>0</v>
       </c>
       <c r="L406" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M406" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0">
-        <v>6410</v>
+        <v>7248</v>
       </c>
       <c r="B407" s="0" t="s">
         <v>286</v>
@@ -18486,15 +18498,15 @@
         <v>0</v>
       </c>
       <c r="L407" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M407" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0">
-        <v>7319</v>
+        <v>6410</v>
       </c>
       <c r="B408" s="0" t="s">
         <v>286</v>
@@ -18527,27 +18539,27 @@
         <v>0</v>
       </c>
       <c r="L408" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M408" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0">
-        <v>7276</v>
+        <v>7319</v>
       </c>
       <c r="B409" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>341</v>
+        <v>291</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>464</v>
       </c>
       <c r="E409" s="0" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F409" s="0">
         <v>1</v>
@@ -18568,27 +18580,27 @@
         <v>0</v>
       </c>
       <c r="L409" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M409" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="0">
-        <v>7157</v>
+        <v>7276</v>
       </c>
       <c r="B410" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>465</v>
       </c>
       <c r="E410" s="0" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F410" s="0">
         <v>1</v>
@@ -18609,27 +18621,27 @@
         <v>0</v>
       </c>
       <c r="L410" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M410" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0">
-        <v>5007</v>
+        <v>7157</v>
       </c>
       <c r="B411" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>466</v>
       </c>
       <c r="E411" s="0" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F411" s="0">
         <v>1</v>
@@ -18650,21 +18662,21 @@
         <v>0</v>
       </c>
       <c r="L411" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M411" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0">
-        <v>6889</v>
+        <v>5007</v>
       </c>
       <c r="B412" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>467</v>
@@ -18699,19 +18711,19 @@
     </row>
     <row r="413">
       <c r="A413" s="0">
-        <v>7392</v>
+        <v>6889</v>
       </c>
       <c r="B413" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>468</v>
       </c>
       <c r="E413" s="0" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F413" s="0">
         <v>1</v>
@@ -18732,15 +18744,15 @@
         <v>0</v>
       </c>
       <c r="L413" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M413" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0">
-        <v>6212</v>
+        <v>7392</v>
       </c>
       <c r="B414" s="0" t="s">
         <v>286</v>
@@ -18773,27 +18785,27 @@
         <v>0</v>
       </c>
       <c r="L414" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M414" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="0">
-        <v>7481</v>
+        <v>6212</v>
       </c>
       <c r="B415" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>470</v>
       </c>
       <c r="E415" s="0" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F415" s="0">
         <v>1</v>
@@ -18814,103 +18826,103 @@
         <v>0</v>
       </c>
       <c r="L415" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M415" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0">
-        <v>2764</v>
+        <v>7481</v>
       </c>
       <c r="B416" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C416" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="D416" s="0" t="s">
         <v>471</v>
       </c>
-      <c r="C416" s="0" t="s">
-        <v>472</v>
-      </c>
-      <c r="D416" s="0" t="s">
-        <v>473</v>
-      </c>
       <c r="E416" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F416" s="0">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G416" s="0">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H416" s="0">
         <v>0</v>
       </c>
       <c r="I416" s="0">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J416" s="0">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K416" s="0">
         <v>0</v>
       </c>
       <c r="L416" s="0">
-        <v>370</v>
+        <v>1</v>
       </c>
       <c r="M416" s="0">
-        <v>370</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0">
-        <v>5585</v>
+        <v>6592</v>
       </c>
       <c r="B417" s="0" t="s">
-        <v>471</v>
+        <v>286</v>
       </c>
       <c r="C417" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="D417" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="D417" s="0" t="s">
-        <v>474</v>
-      </c>
       <c r="E417" s="0" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F417" s="0">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G417" s="0">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H417" s="0">
         <v>0</v>
       </c>
       <c r="I417" s="0">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="J417" s="0">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K417" s="0">
         <v>0</v>
       </c>
       <c r="L417" s="0">
-        <v>365</v>
+        <v>1</v>
       </c>
       <c r="M417" s="0">
-        <v>365</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0">
-        <v>4871</v>
+        <v>2764</v>
       </c>
       <c r="B418" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>475</v>
@@ -18919,203 +18931,203 @@
         <v>19</v>
       </c>
       <c r="F418" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G418" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H418" s="0">
         <v>0</v>
       </c>
       <c r="I418" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J418" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K418" s="0">
         <v>0</v>
       </c>
       <c r="L418" s="0">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="M418" s="0">
-        <v>280</v>
+        <v>370</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0">
-        <v>6052</v>
+        <v>5585</v>
       </c>
       <c r="B419" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>476</v>
       </c>
       <c r="E419" s="0" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F419" s="0">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G419" s="0">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H419" s="0">
         <v>0</v>
       </c>
       <c r="I419" s="0">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J419" s="0">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K419" s="0">
         <v>0</v>
       </c>
       <c r="L419" s="0">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="M419" s="0">
-        <v>271</v>
+        <v>365</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0">
-        <v>6397</v>
+        <v>4871</v>
       </c>
       <c r="B420" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>477</v>
       </c>
       <c r="E420" s="0" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F420" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G420" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H420" s="0">
         <v>0</v>
       </c>
       <c r="I420" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J420" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K420" s="0">
         <v>0</v>
       </c>
       <c r="L420" s="0">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="M420" s="0">
-        <v>232</v>
+        <v>280</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0">
-        <v>5951</v>
+        <v>6052</v>
       </c>
       <c r="B421" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>478</v>
       </c>
       <c r="E421" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F421" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G421" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H421" s="0">
         <v>0</v>
       </c>
       <c r="I421" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J421" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K421" s="0">
         <v>0</v>
       </c>
       <c r="L421" s="0">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="M421" s="0">
-        <v>225</v>
+        <v>271</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0">
-        <v>2097</v>
+        <v>6397</v>
       </c>
       <c r="B422" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>479</v>
       </c>
       <c r="E422" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F422" s="0">
         <v>27</v>
       </c>
-      <c r="F422" s="0">
-        <v>25</v>
-      </c>
       <c r="G422" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H422" s="0">
         <v>0</v>
       </c>
       <c r="I422" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J422" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K422" s="0">
         <v>0</v>
       </c>
       <c r="L422" s="0">
-        <v>200</v>
+        <v>232</v>
       </c>
       <c r="M422" s="0">
-        <v>197</v>
+        <v>232</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0">
-        <v>6434</v>
+        <v>5951</v>
       </c>
       <c r="B423" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>480</v>
@@ -19124,162 +19136,162 @@
         <v>35</v>
       </c>
       <c r="F423" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G423" s="0">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H423" s="0">
         <v>0</v>
       </c>
       <c r="I423" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J423" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K423" s="0">
         <v>0</v>
       </c>
       <c r="L423" s="0">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="M423" s="0">
-        <v>190</v>
+        <v>225</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0">
-        <v>7017</v>
+        <v>2097</v>
       </c>
       <c r="B424" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>481</v>
       </c>
       <c r="E424" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F424" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G424" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H424" s="0">
         <v>0</v>
       </c>
       <c r="I424" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J424" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K424" s="0">
         <v>0</v>
       </c>
       <c r="L424" s="0">
-        <v>157</v>
+        <v>200</v>
       </c>
       <c r="M424" s="0">
-        <v>154</v>
+        <v>197</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0">
-        <v>2137</v>
+        <v>6434</v>
       </c>
       <c r="B425" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>482</v>
       </c>
       <c r="E425" s="0" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F425" s="0">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G425" s="0">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H425" s="0">
         <v>0</v>
       </c>
       <c r="I425" s="0">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J425" s="0">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K425" s="0">
         <v>0</v>
       </c>
       <c r="L425" s="0">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="M425" s="0">
-        <v>128</v>
+        <v>190</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0">
-        <v>5637</v>
+        <v>7017</v>
       </c>
       <c r="B426" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>483</v>
       </c>
       <c r="E426" s="0" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F426" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G426" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H426" s="0">
         <v>0</v>
       </c>
       <c r="I426" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J426" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K426" s="0">
         <v>0</v>
       </c>
       <c r="L426" s="0">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="M426" s="0">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0">
-        <v>6435</v>
+        <v>2137</v>
       </c>
       <c r="B427" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>484</v>
@@ -19288,51 +19300,51 @@
         <v>21</v>
       </c>
       <c r="F427" s="0">
+        <v>19</v>
+      </c>
+      <c r="G427" s="0">
+        <v>19</v>
+      </c>
+      <c r="H427" s="0">
+        <v>0</v>
+      </c>
+      <c r="I427" s="0">
         <v>18</v>
       </c>
-      <c r="G427" s="0">
+      <c r="J427" s="0">
         <v>18</v>
       </c>
-      <c r="H427" s="0">
-        <v>0</v>
-      </c>
-      <c r="I427" s="0">
-        <v>17</v>
-      </c>
-      <c r="J427" s="0">
-        <v>17</v>
-      </c>
       <c r="K427" s="0">
         <v>0</v>
       </c>
       <c r="L427" s="0">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="M427" s="0">
-        <v>92</v>
+        <v>128</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0">
-        <v>4510</v>
+        <v>5637</v>
       </c>
       <c r="B428" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>485</v>
       </c>
       <c r="E428" s="0" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F428" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G428" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H428" s="0">
         <v>0</v>
@@ -19347,27 +19359,27 @@
         <v>0</v>
       </c>
       <c r="L428" s="0">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M428" s="0">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0">
-        <v>531</v>
+        <v>6435</v>
       </c>
       <c r="B429" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>486</v>
       </c>
       <c r="E429" s="0" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F429" s="0">
         <v>18</v>
@@ -19379,206 +19391,206 @@
         <v>0</v>
       </c>
       <c r="I429" s="0">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J429" s="0">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K429" s="0">
         <v>0</v>
       </c>
       <c r="L429" s="0">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="M429" s="0">
-        <v>118</v>
+        <v>92</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0">
-        <v>5995</v>
+        <v>4510</v>
       </c>
       <c r="B430" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>487</v>
       </c>
       <c r="E430" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F430" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G430" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H430" s="0">
         <v>0</v>
       </c>
       <c r="I430" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J430" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K430" s="0">
         <v>0</v>
       </c>
       <c r="L430" s="0">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="M430" s="0">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0">
-        <v>6675</v>
+        <v>531</v>
       </c>
       <c r="B431" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>488</v>
       </c>
       <c r="E431" s="0" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F431" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G431" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H431" s="0">
         <v>0</v>
       </c>
       <c r="I431" s="0">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J431" s="0">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K431" s="0">
         <v>0</v>
       </c>
       <c r="L431" s="0">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="M431" s="0">
-        <v>70</v>
+        <v>118</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="0">
-        <v>7071</v>
+        <v>5995</v>
       </c>
       <c r="B432" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>489</v>
       </c>
       <c r="E432" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F432" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G432" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H432" s="0">
         <v>0</v>
       </c>
       <c r="I432" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J432" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K432" s="0">
         <v>0</v>
       </c>
       <c r="L432" s="0">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="M432" s="0">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0">
-        <v>7023</v>
+        <v>6675</v>
       </c>
       <c r="B433" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>490</v>
       </c>
       <c r="E433" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F433" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G433" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H433" s="0">
         <v>0</v>
       </c>
       <c r="I433" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J433" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K433" s="0">
         <v>0</v>
       </c>
       <c r="L433" s="0">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="M433" s="0">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0">
-        <v>6060</v>
+        <v>7071</v>
       </c>
       <c r="B434" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>491</v>
       </c>
       <c r="E434" s="0" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="F434" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G434" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H434" s="0">
         <v>0</v>
@@ -19593,27 +19605,27 @@
         <v>0</v>
       </c>
       <c r="L434" s="0">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="M434" s="0">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0">
-        <v>2061</v>
+        <v>7023</v>
       </c>
       <c r="B435" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>492</v>
       </c>
       <c r="E435" s="0" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="F435" s="0">
         <v>15</v>
@@ -19634,74 +19646,74 @@
         <v>0</v>
       </c>
       <c r="L435" s="0">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="M435" s="0">
-        <v>79</v>
+        <v>57</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0">
-        <v>7351</v>
+        <v>6060</v>
       </c>
       <c r="B436" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>493</v>
       </c>
       <c r="E436" s="0" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F436" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G436" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H436" s="0">
         <v>0</v>
       </c>
       <c r="I436" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J436" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K436" s="0">
         <v>0</v>
       </c>
       <c r="L436" s="0">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="M436" s="0">
-        <v>57</v>
+        <v>91</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0">
-        <v>309</v>
+        <v>2061</v>
       </c>
       <c r="B437" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>494</v>
       </c>
       <c r="E437" s="0" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F437" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G437" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H437" s="0">
         <v>0</v>
@@ -19716,27 +19728,27 @@
         <v>0</v>
       </c>
       <c r="L437" s="0">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="M437" s="0">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0">
-        <v>6572</v>
+        <v>7351</v>
       </c>
       <c r="B438" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>495</v>
       </c>
       <c r="E438" s="0" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F438" s="0">
         <v>14</v>
@@ -19748,118 +19760,118 @@
         <v>0</v>
       </c>
       <c r="I438" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J438" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K438" s="0">
         <v>0</v>
       </c>
       <c r="L438" s="0">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="M438" s="0">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0">
-        <v>4371</v>
+        <v>309</v>
       </c>
       <c r="B439" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>496</v>
       </c>
       <c r="E439" s="0" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F439" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G439" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H439" s="0">
         <v>0</v>
       </c>
       <c r="I439" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J439" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K439" s="0">
         <v>0</v>
       </c>
       <c r="L439" s="0">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M439" s="0">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0">
-        <v>4463</v>
+        <v>6572</v>
       </c>
       <c r="B440" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>497</v>
       </c>
       <c r="E440" s="0" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F440" s="0">
+        <v>14</v>
+      </c>
+      <c r="G440" s="0">
+        <v>14</v>
+      </c>
+      <c r="H440" s="0">
+        <v>0</v>
+      </c>
+      <c r="I440" s="0">
         <v>13</v>
       </c>
-      <c r="G440" s="0">
+      <c r="J440" s="0">
         <v>13</v>
       </c>
-      <c r="H440" s="0">
-        <v>0</v>
-      </c>
-      <c r="I440" s="0">
-        <v>14</v>
-      </c>
-      <c r="J440" s="0">
-        <v>14</v>
-      </c>
       <c r="K440" s="0">
         <v>0</v>
       </c>
       <c r="L440" s="0">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="M440" s="0">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0">
-        <v>4728</v>
+        <v>4371</v>
       </c>
       <c r="B441" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>498</v>
       </c>
       <c r="E441" s="0" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F441" s="0">
         <v>13</v>
@@ -19880,27 +19892,27 @@
         <v>0</v>
       </c>
       <c r="L441" s="0">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="M441" s="0">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0">
-        <v>2038</v>
+        <v>4463</v>
       </c>
       <c r="B442" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>499</v>
       </c>
       <c r="E442" s="0" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F442" s="0">
         <v>13</v>
@@ -19912,36 +19924,36 @@
         <v>0</v>
       </c>
       <c r="I442" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J442" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K442" s="0">
         <v>0</v>
       </c>
       <c r="L442" s="0">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M442" s="0">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0">
-        <v>7547</v>
+        <v>4728</v>
       </c>
       <c r="B443" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>500</v>
       </c>
       <c r="E443" s="0" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F443" s="0">
         <v>13</v>
@@ -19953,200 +19965,200 @@
         <v>0</v>
       </c>
       <c r="I443" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J443" s="0">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K443" s="0">
         <v>0</v>
       </c>
       <c r="L443" s="0">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="M443" s="0">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0">
-        <v>5734</v>
+        <v>2038</v>
       </c>
       <c r="B444" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>501</v>
       </c>
       <c r="E444" s="0" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F444" s="0">
+        <v>13</v>
+      </c>
+      <c r="G444" s="0">
+        <v>13</v>
+      </c>
+      <c r="H444" s="0">
+        <v>0</v>
+      </c>
+      <c r="I444" s="0">
         <v>12</v>
       </c>
-      <c r="G444" s="0">
+      <c r="J444" s="0">
         <v>12</v>
       </c>
-      <c r="H444" s="0">
-        <v>0</v>
-      </c>
-      <c r="I444" s="0">
-        <v>13</v>
-      </c>
-      <c r="J444" s="0">
-        <v>13</v>
-      </c>
       <c r="K444" s="0">
         <v>0</v>
       </c>
       <c r="L444" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M444" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0">
-        <v>7484</v>
+        <v>7547</v>
       </c>
       <c r="B445" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>502</v>
       </c>
       <c r="E445" s="0" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F445" s="0">
+        <v>13</v>
+      </c>
+      <c r="G445" s="0">
+        <v>13</v>
+      </c>
+      <c r="H445" s="0">
+        <v>0</v>
+      </c>
+      <c r="I445" s="0">
         <v>12</v>
       </c>
-      <c r="G445" s="0">
+      <c r="J445" s="0">
         <v>12</v>
       </c>
-      <c r="H445" s="0">
-        <v>0</v>
-      </c>
-      <c r="I445" s="0">
-        <v>11</v>
-      </c>
-      <c r="J445" s="0">
-        <v>11</v>
-      </c>
       <c r="K445" s="0">
         <v>0</v>
       </c>
       <c r="L445" s="0">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M445" s="0">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0">
-        <v>6967</v>
+        <v>5734</v>
       </c>
       <c r="B446" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>503</v>
       </c>
       <c r="E446" s="0" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F446" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G446" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H446" s="0">
         <v>0</v>
       </c>
       <c r="I446" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J446" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K446" s="0">
         <v>0</v>
       </c>
       <c r="L446" s="0">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M446" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0">
-        <v>4923</v>
+        <v>7484</v>
       </c>
       <c r="B447" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>504</v>
       </c>
       <c r="E447" s="0" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F447" s="0">
+        <v>12</v>
+      </c>
+      <c r="G447" s="0">
+        <v>12</v>
+      </c>
+      <c r="H447" s="0">
+        <v>0</v>
+      </c>
+      <c r="I447" s="0">
         <v>11</v>
       </c>
-      <c r="G447" s="0">
+      <c r="J447" s="0">
         <v>11</v>
       </c>
-      <c r="H447" s="0">
-        <v>0</v>
-      </c>
-      <c r="I447" s="0">
-        <v>10</v>
-      </c>
-      <c r="J447" s="0">
-        <v>10</v>
-      </c>
       <c r="K447" s="0">
         <v>0</v>
       </c>
       <c r="L447" s="0">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M447" s="0">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0">
-        <v>6229</v>
+        <v>6967</v>
       </c>
       <c r="B448" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>505</v>
       </c>
       <c r="E448" s="0" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F448" s="0">
         <v>11</v>
@@ -20158,118 +20170,118 @@
         <v>0</v>
       </c>
       <c r="I448" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J448" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K448" s="0">
         <v>0</v>
       </c>
       <c r="L448" s="0">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M448" s="0">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0">
-        <v>5672</v>
+        <v>4923</v>
       </c>
       <c r="B449" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>506</v>
       </c>
       <c r="E449" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F449" s="0">
+        <v>11</v>
+      </c>
+      <c r="G449" s="0">
+        <v>11</v>
+      </c>
+      <c r="H449" s="0">
+        <v>0</v>
+      </c>
+      <c r="I449" s="0">
         <v>10</v>
       </c>
-      <c r="G449" s="0">
+      <c r="J449" s="0">
         <v>10</v>
       </c>
-      <c r="H449" s="0">
-        <v>0</v>
-      </c>
-      <c r="I449" s="0">
-        <v>11</v>
-      </c>
-      <c r="J449" s="0">
-        <v>11</v>
-      </c>
       <c r="K449" s="0">
         <v>0</v>
       </c>
       <c r="L449" s="0">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="M449" s="0">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0">
-        <v>7313</v>
+        <v>6229</v>
       </c>
       <c r="B450" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>507</v>
       </c>
       <c r="E450" s="0" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F450" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G450" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H450" s="0">
         <v>0</v>
       </c>
       <c r="I450" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J450" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K450" s="0">
         <v>0</v>
       </c>
       <c r="L450" s="0">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M450" s="0">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0">
-        <v>7347</v>
+        <v>5672</v>
       </c>
       <c r="B451" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>508</v>
       </c>
       <c r="E451" s="0" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F451" s="0">
         <v>10</v>
@@ -20281,36 +20293,36 @@
         <v>0</v>
       </c>
       <c r="I451" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J451" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K451" s="0">
         <v>0</v>
       </c>
       <c r="L451" s="0">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M451" s="0">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0">
-        <v>7554</v>
+        <v>7313</v>
       </c>
       <c r="B452" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>509</v>
       </c>
       <c r="E452" s="0" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F452" s="0">
         <v>10</v>
@@ -20322,118 +20334,118 @@
         <v>0</v>
       </c>
       <c r="I452" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J452" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K452" s="0">
         <v>0</v>
       </c>
       <c r="L452" s="0">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="M452" s="0">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0">
-        <v>6530</v>
+        <v>7347</v>
       </c>
       <c r="B453" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>510</v>
       </c>
       <c r="E453" s="0" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F453" s="0">
+        <v>10</v>
+      </c>
+      <c r="G453" s="0">
+        <v>10</v>
+      </c>
+      <c r="H453" s="0">
+        <v>0</v>
+      </c>
+      <c r="I453" s="0">
         <v>9</v>
       </c>
-      <c r="G453" s="0">
+      <c r="J453" s="0">
         <v>9</v>
       </c>
-      <c r="H453" s="0">
-        <v>0</v>
-      </c>
-      <c r="I453" s="0">
-        <v>10</v>
-      </c>
-      <c r="J453" s="0">
-        <v>10</v>
-      </c>
       <c r="K453" s="0">
         <v>0</v>
       </c>
       <c r="L453" s="0">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M453" s="0">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0">
-        <v>5544</v>
+        <v>7554</v>
       </c>
       <c r="B454" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>511</v>
       </c>
       <c r="E454" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F454" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G454" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H454" s="0">
         <v>0</v>
       </c>
       <c r="I454" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J454" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K454" s="0">
         <v>0</v>
       </c>
       <c r="L454" s="0">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M454" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0">
-        <v>5029</v>
+        <v>6530</v>
       </c>
       <c r="B455" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>512</v>
       </c>
       <c r="E455" s="0" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F455" s="0">
         <v>9</v>
@@ -20445,36 +20457,36 @@
         <v>0</v>
       </c>
       <c r="I455" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J455" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K455" s="0">
         <v>0</v>
       </c>
       <c r="L455" s="0">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M455" s="0">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0">
-        <v>2155</v>
+        <v>5544</v>
       </c>
       <c r="B456" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>513</v>
       </c>
       <c r="E456" s="0" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F456" s="0">
         <v>9</v>
@@ -20495,27 +20507,27 @@
         <v>0</v>
       </c>
       <c r="L456" s="0">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M456" s="0">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="0">
-        <v>6646</v>
+        <v>5029</v>
       </c>
       <c r="B457" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>514</v>
       </c>
       <c r="E457" s="0" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="F457" s="0">
         <v>9</v>
@@ -20527,118 +20539,118 @@
         <v>0</v>
       </c>
       <c r="I457" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J457" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K457" s="0">
         <v>0</v>
       </c>
       <c r="L457" s="0">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M457" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0">
-        <v>6643</v>
+        <v>2155</v>
       </c>
       <c r="B458" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>515</v>
       </c>
       <c r="E458" s="0" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="F458" s="0">
+        <v>9</v>
+      </c>
+      <c r="G458" s="0">
+        <v>9</v>
+      </c>
+      <c r="H458" s="0">
+        <v>0</v>
+      </c>
+      <c r="I458" s="0">
         <v>8</v>
       </c>
-      <c r="G458" s="0">
+      <c r="J458" s="0">
         <v>8</v>
       </c>
-      <c r="H458" s="0">
-        <v>0</v>
-      </c>
-      <c r="I458" s="0">
-        <v>7</v>
-      </c>
-      <c r="J458" s="0">
-        <v>7</v>
-      </c>
       <c r="K458" s="0">
         <v>0</v>
       </c>
       <c r="L458" s="0">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="M458" s="0">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0">
-        <v>4359</v>
+        <v>6646</v>
       </c>
       <c r="B459" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>516</v>
       </c>
       <c r="E459" s="0" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="F459" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G459" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H459" s="0">
         <v>0</v>
       </c>
       <c r="I459" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J459" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K459" s="0">
         <v>0</v>
       </c>
       <c r="L459" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M459" s="0">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0">
-        <v>6164</v>
+        <v>6643</v>
       </c>
       <c r="B460" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>517</v>
       </c>
       <c r="E460" s="0" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F460" s="0">
         <v>8</v>
@@ -20650,36 +20662,36 @@
         <v>0</v>
       </c>
       <c r="I460" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J460" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K460" s="0">
         <v>0</v>
       </c>
       <c r="L460" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M460" s="0">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0">
-        <v>6904</v>
+        <v>4359</v>
       </c>
       <c r="B461" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>518</v>
       </c>
       <c r="E461" s="0" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F461" s="0">
         <v>8</v>
@@ -20691,36 +20703,36 @@
         <v>0</v>
       </c>
       <c r="I461" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J461" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K461" s="0">
         <v>0</v>
       </c>
       <c r="L461" s="0">
+        <v>31</v>
+      </c>
+      <c r="M461" s="0">
         <v>28</v>
-      </c>
-      <c r="M461" s="0">
-        <v>29</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0">
-        <v>7449</v>
+        <v>6164</v>
       </c>
       <c r="B462" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>519</v>
       </c>
       <c r="E462" s="0" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F462" s="0">
         <v>8</v>
@@ -20732,10 +20744,10 @@
         <v>0</v>
       </c>
       <c r="I462" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J462" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K462" s="0">
         <v>0</v>
@@ -20744,106 +20756,106 @@
         <v>20</v>
       </c>
       <c r="M462" s="0">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0">
-        <v>5436</v>
+        <v>6904</v>
       </c>
       <c r="B463" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>520</v>
       </c>
       <c r="E463" s="0" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F463" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G463" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H463" s="0">
         <v>0</v>
       </c>
       <c r="I463" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J463" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K463" s="0">
         <v>0</v>
       </c>
       <c r="L463" s="0">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M463" s="0">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0">
-        <v>6669</v>
+        <v>7449</v>
       </c>
       <c r="B464" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>521</v>
       </c>
       <c r="E464" s="0" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F464" s="0">
+        <v>8</v>
+      </c>
+      <c r="G464" s="0">
+        <v>8</v>
+      </c>
+      <c r="H464" s="0">
+        <v>0</v>
+      </c>
+      <c r="I464" s="0">
         <v>7</v>
       </c>
-      <c r="G464" s="0">
+      <c r="J464" s="0">
         <v>7</v>
       </c>
-      <c r="H464" s="0">
-        <v>0</v>
-      </c>
-      <c r="I464" s="0">
-        <v>6</v>
-      </c>
-      <c r="J464" s="0">
-        <v>6</v>
-      </c>
       <c r="K464" s="0">
         <v>0</v>
       </c>
       <c r="L464" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M464" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0">
-        <v>7252</v>
+        <v>5436</v>
       </c>
       <c r="B465" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>522</v>
       </c>
       <c r="E465" s="0" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F465" s="0">
         <v>7</v>
@@ -20864,27 +20876,27 @@
         <v>0</v>
       </c>
       <c r="L465" s="0">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M465" s="0">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0">
-        <v>608</v>
+        <v>6669</v>
       </c>
       <c r="B466" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>523</v>
       </c>
       <c r="E466" s="0" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="F466" s="0">
         <v>7</v>
@@ -20905,33 +20917,33 @@
         <v>0</v>
       </c>
       <c r="L466" s="0">
+        <v>21</v>
+      </c>
+      <c r="M466" s="0">
         <v>18</v>
-      </c>
-      <c r="M466" s="0">
-        <v>16</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0">
-        <v>5918</v>
+        <v>7252</v>
       </c>
       <c r="B467" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>524</v>
       </c>
       <c r="E467" s="0" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F467" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G467" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H467" s="0">
         <v>0</v>
@@ -20946,33 +20958,33 @@
         <v>0</v>
       </c>
       <c r="L467" s="0">
+        <v>18</v>
+      </c>
+      <c r="M467" s="0">
         <v>16</v>
-      </c>
-      <c r="M467" s="0">
-        <v>17</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0">
-        <v>6598</v>
+        <v>608</v>
       </c>
       <c r="B468" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>525</v>
       </c>
       <c r="E468" s="0" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="F468" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G468" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H468" s="0">
         <v>0</v>
@@ -20987,27 +20999,27 @@
         <v>0</v>
       </c>
       <c r="L468" s="0">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M468" s="0">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0">
-        <v>2832</v>
+        <v>5918</v>
       </c>
       <c r="B469" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>526</v>
       </c>
       <c r="E469" s="0" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F469" s="0">
         <v>6</v>
@@ -21019,36 +21031,36 @@
         <v>0</v>
       </c>
       <c r="I469" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J469" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K469" s="0">
         <v>0</v>
       </c>
       <c r="L469" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M469" s="0">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0">
-        <v>6556</v>
+        <v>6598</v>
       </c>
       <c r="B470" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>527</v>
       </c>
       <c r="E470" s="0" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F470" s="0">
         <v>6</v>
@@ -21069,27 +21081,27 @@
         <v>0</v>
       </c>
       <c r="L470" s="0">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M470" s="0">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0">
-        <v>7008</v>
+        <v>2832</v>
       </c>
       <c r="B471" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D471" s="0" t="s">
         <v>528</v>
       </c>
       <c r="E471" s="0" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F471" s="0">
         <v>6</v>
@@ -21101,36 +21113,36 @@
         <v>0</v>
       </c>
       <c r="I471" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J471" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K471" s="0">
         <v>0</v>
       </c>
       <c r="L471" s="0">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M471" s="0">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0">
-        <v>6831</v>
+        <v>6556</v>
       </c>
       <c r="B472" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>529</v>
       </c>
       <c r="E472" s="0" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F472" s="0">
         <v>6</v>
@@ -21142,118 +21154,118 @@
         <v>0</v>
       </c>
       <c r="I472" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J472" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K472" s="0">
         <v>0</v>
       </c>
       <c r="L472" s="0">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="M472" s="0">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0">
-        <v>4896</v>
+        <v>7008</v>
       </c>
       <c r="B473" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>287</v>
+        <v>474</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>530</v>
       </c>
       <c r="E473" s="0" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F473" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G473" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H473" s="0">
         <v>0</v>
       </c>
       <c r="I473" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J473" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K473" s="0">
         <v>0</v>
       </c>
       <c r="L473" s="0">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M473" s="0">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="0">
-        <v>6519</v>
+        <v>6831</v>
       </c>
       <c r="B474" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>531</v>
       </c>
       <c r="E474" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F474" s="0">
+        <v>6</v>
+      </c>
+      <c r="G474" s="0">
+        <v>6</v>
+      </c>
+      <c r="H474" s="0">
+        <v>0</v>
+      </c>
+      <c r="I474" s="0">
+        <v>7</v>
+      </c>
+      <c r="J474" s="0">
+        <v>7</v>
+      </c>
+      <c r="K474" s="0">
+        <v>0</v>
+      </c>
+      <c r="L474" s="0">
+        <v>22</v>
+      </c>
+      <c r="M474" s="0">
         <v>25</v>
-      </c>
-      <c r="F474" s="0">
-        <v>5</v>
-      </c>
-      <c r="G474" s="0">
-        <v>5</v>
-      </c>
-      <c r="H474" s="0">
-        <v>0</v>
-      </c>
-      <c r="I474" s="0">
-        <v>4</v>
-      </c>
-      <c r="J474" s="0">
-        <v>4</v>
-      </c>
-      <c r="K474" s="0">
-        <v>0</v>
-      </c>
-      <c r="L474" s="0">
-        <v>20</v>
-      </c>
-      <c r="M474" s="0">
-        <v>17</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0">
-        <v>5882</v>
+        <v>4896</v>
       </c>
       <c r="B475" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>471</v>
+        <v>287</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>532</v>
       </c>
       <c r="E475" s="0" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F475" s="0">
         <v>5</v>
@@ -21265,36 +21277,36 @@
         <v>0</v>
       </c>
       <c r="I475" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J475" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K475" s="0">
         <v>0</v>
       </c>
       <c r="L475" s="0">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M475" s="0">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="0">
-        <v>7213</v>
+        <v>6519</v>
       </c>
       <c r="B476" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>533</v>
       </c>
       <c r="E476" s="0" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F476" s="0">
         <v>5</v>
@@ -21306,36 +21318,36 @@
         <v>0</v>
       </c>
       <c r="I476" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J476" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K476" s="0">
         <v>0</v>
       </c>
       <c r="L476" s="0">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M476" s="0">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="0">
-        <v>4387</v>
+        <v>5882</v>
       </c>
       <c r="B477" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>534</v>
       </c>
       <c r="E477" s="0" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F477" s="0">
         <v>5</v>
@@ -21347,159 +21359,159 @@
         <v>0</v>
       </c>
       <c r="I477" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J477" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K477" s="0">
         <v>0</v>
       </c>
       <c r="L477" s="0">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M477" s="0">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0">
-        <v>6243</v>
+        <v>7213</v>
       </c>
       <c r="B478" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>535</v>
       </c>
       <c r="E478" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F478" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G478" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H478" s="0">
         <v>0</v>
       </c>
       <c r="I478" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J478" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K478" s="0">
         <v>0</v>
       </c>
       <c r="L478" s="0">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M478" s="0">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0">
-        <v>7374</v>
+        <v>4387</v>
       </c>
       <c r="B479" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>536</v>
       </c>
       <c r="E479" s="0" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F479" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G479" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H479" s="0">
         <v>0</v>
       </c>
       <c r="I479" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J479" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K479" s="0">
         <v>0</v>
       </c>
       <c r="L479" s="0">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M479" s="0">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="0">
-        <v>313</v>
+        <v>2012</v>
       </c>
       <c r="B480" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>537</v>
       </c>
       <c r="E480" s="0" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F480" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G480" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H480" s="0">
         <v>0</v>
       </c>
       <c r="I480" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J480" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K480" s="0">
         <v>0</v>
       </c>
       <c r="L480" s="0">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M480" s="0">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="0">
-        <v>6204</v>
+        <v>6243</v>
       </c>
       <c r="B481" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>538</v>
       </c>
       <c r="E481" s="0" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F481" s="0">
         <v>4</v>
@@ -21511,36 +21523,36 @@
         <v>0</v>
       </c>
       <c r="I481" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J481" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K481" s="0">
         <v>0</v>
       </c>
       <c r="L481" s="0">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M481" s="0">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0">
-        <v>7453</v>
+        <v>7374</v>
       </c>
       <c r="B482" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>539</v>
       </c>
       <c r="E482" s="0" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F482" s="0">
         <v>4</v>
@@ -21569,19 +21581,19 @@
     </row>
     <row r="483">
       <c r="A483" s="0">
-        <v>7162</v>
+        <v>313</v>
       </c>
       <c r="B483" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>540</v>
       </c>
       <c r="E483" s="0" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F483" s="0">
         <v>4</v>
@@ -21593,10 +21605,10 @@
         <v>0</v>
       </c>
       <c r="I483" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J483" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K483" s="0">
         <v>0</v>
@@ -21605,24 +21617,24 @@
         <v>10</v>
       </c>
       <c r="M483" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="0">
-        <v>7349</v>
+        <v>6204</v>
       </c>
       <c r="B484" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>541</v>
       </c>
       <c r="E484" s="0" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="F484" s="0">
         <v>4</v>
@@ -21634,36 +21646,36 @@
         <v>0</v>
       </c>
       <c r="I484" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J484" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K484" s="0">
         <v>0</v>
       </c>
       <c r="L484" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M484" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="0">
-        <v>7272</v>
+        <v>7453</v>
       </c>
       <c r="B485" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>542</v>
       </c>
       <c r="E485" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F485" s="0">
         <v>4</v>
@@ -21684,27 +21696,27 @@
         <v>0</v>
       </c>
       <c r="L485" s="0">
+        <v>9</v>
+      </c>
+      <c r="M485" s="0">
         <v>7</v>
-      </c>
-      <c r="M485" s="0">
-        <v>6</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="0">
-        <v>7546</v>
+        <v>7162</v>
       </c>
       <c r="B486" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>543</v>
       </c>
       <c r="E486" s="0" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F486" s="0">
         <v>4</v>
@@ -21733,40 +21745,40 @@
     </row>
     <row r="487">
       <c r="A487" s="0">
-        <v>7128</v>
+        <v>7349</v>
       </c>
       <c r="B487" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>544</v>
       </c>
       <c r="E487" s="0" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="F487" s="0">
+        <v>4</v>
+      </c>
+      <c r="G487" s="0">
+        <v>4</v>
+      </c>
+      <c r="H487" s="0">
+        <v>0</v>
+      </c>
+      <c r="I487" s="0">
         <v>3</v>
       </c>
-      <c r="G487" s="0">
+      <c r="J487" s="0">
         <v>3</v>
       </c>
-      <c r="H487" s="0">
-        <v>0</v>
-      </c>
-      <c r="I487" s="0">
-        <v>4</v>
-      </c>
-      <c r="J487" s="0">
-        <v>4</v>
-      </c>
       <c r="K487" s="0">
         <v>0</v>
       </c>
       <c r="L487" s="0">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M487" s="0">
         <v>7</v>
@@ -21774,25 +21786,25 @@
     </row>
     <row r="488">
       <c r="A488" s="0">
-        <v>6822</v>
+        <v>7272</v>
       </c>
       <c r="B488" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>545</v>
       </c>
       <c r="E488" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F488" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G488" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H488" s="0">
         <v>0</v>
@@ -21807,33 +21819,33 @@
         <v>0</v>
       </c>
       <c r="L488" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M488" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="0">
-        <v>7001</v>
+        <v>7546</v>
       </c>
       <c r="B489" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D489" s="0" t="s">
         <v>546</v>
       </c>
       <c r="E489" s="0" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F489" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G489" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H489" s="0">
         <v>0</v>
@@ -21848,27 +21860,27 @@
         <v>0</v>
       </c>
       <c r="L489" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M489" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0">
-        <v>7523</v>
+        <v>7128</v>
       </c>
       <c r="B490" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>547</v>
       </c>
       <c r="E490" s="0" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F490" s="0">
         <v>3</v>
@@ -21880,36 +21892,36 @@
         <v>0</v>
       </c>
       <c r="I490" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J490" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K490" s="0">
         <v>0</v>
       </c>
       <c r="L490" s="0">
+        <v>5</v>
+      </c>
+      <c r="M490" s="0">
         <v>7</v>
-      </c>
-      <c r="M490" s="0">
-        <v>6</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="0">
-        <v>7120</v>
+        <v>6822</v>
       </c>
       <c r="B491" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D491" s="0" t="s">
         <v>548</v>
       </c>
       <c r="E491" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F491" s="0">
         <v>3</v>
@@ -21938,19 +21950,19 @@
     </row>
     <row r="492">
       <c r="A492" s="0">
-        <v>6215</v>
+        <v>7001</v>
       </c>
       <c r="B492" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>549</v>
       </c>
       <c r="E492" s="0" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F492" s="0">
         <v>3</v>
@@ -21962,36 +21974,36 @@
         <v>0</v>
       </c>
       <c r="I492" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J492" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K492" s="0">
         <v>0</v>
       </c>
       <c r="L492" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M492" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="0">
-        <v>7342</v>
+        <v>7523</v>
       </c>
       <c r="B493" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>550</v>
       </c>
       <c r="E493" s="0" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F493" s="0">
         <v>3</v>
@@ -22012,232 +22024,232 @@
         <v>0</v>
       </c>
       <c r="L493" s="0">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M493" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="0">
-        <v>383</v>
+        <v>7120</v>
       </c>
       <c r="B494" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>551</v>
       </c>
       <c r="E494" s="0" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F494" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G494" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H494" s="0">
         <v>0</v>
       </c>
       <c r="I494" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J494" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K494" s="0">
         <v>0</v>
       </c>
       <c r="L494" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M494" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="0">
-        <v>7249</v>
+        <v>6215</v>
       </c>
       <c r="B495" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>552</v>
       </c>
       <c r="E495" s="0" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F495" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G495" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H495" s="0">
         <v>0</v>
       </c>
       <c r="I495" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J495" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K495" s="0">
         <v>0</v>
       </c>
       <c r="L495" s="0">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M495" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="0">
-        <v>7338</v>
+        <v>7342</v>
       </c>
       <c r="B496" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>553</v>
       </c>
       <c r="E496" s="0" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F496" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G496" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H496" s="0">
         <v>0</v>
       </c>
       <c r="I496" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J496" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K496" s="0">
         <v>0</v>
       </c>
       <c r="L496" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M496" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0">
-        <v>7317</v>
+        <v>383</v>
       </c>
       <c r="B497" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D497" s="0" t="s">
         <v>554</v>
       </c>
       <c r="E497" s="0" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F497" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G497" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H497" s="0">
         <v>0</v>
       </c>
       <c r="I497" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J497" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K497" s="0">
         <v>0</v>
       </c>
       <c r="L497" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M497" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="0">
-        <v>7027</v>
+        <v>7249</v>
       </c>
       <c r="B498" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D498" s="0" t="s">
         <v>555</v>
       </c>
       <c r="E498" s="0" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F498" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G498" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H498" s="0">
         <v>0</v>
       </c>
       <c r="I498" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J498" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K498" s="0">
         <v>0</v>
       </c>
       <c r="L498" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M498" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="0">
-        <v>6981</v>
+        <v>7338</v>
       </c>
       <c r="B499" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D499" s="0" t="s">
         <v>556</v>
       </c>
       <c r="E499" s="0" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F499" s="0">
         <v>1</v>
@@ -22258,27 +22270,27 @@
         <v>0</v>
       </c>
       <c r="L499" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M499" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="0">
-        <v>7158</v>
+        <v>7317</v>
       </c>
       <c r="B500" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D500" s="0" t="s">
         <v>557</v>
       </c>
       <c r="E500" s="0" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="F500" s="0">
         <v>1</v>
@@ -22299,27 +22311,27 @@
         <v>0</v>
       </c>
       <c r="L500" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M500" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="0">
-        <v>7161</v>
+        <v>7027</v>
       </c>
       <c r="B501" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D501" s="0" t="s">
         <v>558</v>
       </c>
       <c r="E501" s="0" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F501" s="0">
         <v>1</v>
@@ -22340,27 +22352,27 @@
         <v>0</v>
       </c>
       <c r="L501" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M501" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="0">
-        <v>7408</v>
+        <v>6981</v>
       </c>
       <c r="B502" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="D502" s="0" t="s">
         <v>559</v>
       </c>
       <c r="E502" s="0" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F502" s="0">
         <v>1</v>
@@ -22381,51 +22393,215 @@
         <v>0</v>
       </c>
       <c r="L502" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M502" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="0">
-        <v>7482</v>
+        <v>7158</v>
       </c>
       <c r="B503" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D503" s="0" t="s">
         <v>560</v>
       </c>
       <c r="E503" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F503" s="0">
+        <v>1</v>
+      </c>
+      <c r="G503" s="0">
+        <v>1</v>
+      </c>
+      <c r="H503" s="0">
+        <v>0</v>
+      </c>
+      <c r="I503" s="0">
+        <v>1</v>
+      </c>
+      <c r="J503" s="0">
+        <v>1</v>
+      </c>
+      <c r="K503" s="0">
+        <v>0</v>
+      </c>
+      <c r="L503" s="0">
+        <v>1</v>
+      </c>
+      <c r="M503" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0">
+        <v>7161</v>
+      </c>
+      <c r="B504" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C504" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="D504" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="E504" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F504" s="0">
+        <v>1</v>
+      </c>
+      <c r="G504" s="0">
+        <v>1</v>
+      </c>
+      <c r="H504" s="0">
+        <v>0</v>
+      </c>
+      <c r="I504" s="0">
+        <v>1</v>
+      </c>
+      <c r="J504" s="0">
+        <v>1</v>
+      </c>
+      <c r="K504" s="0">
+        <v>0</v>
+      </c>
+      <c r="L504" s="0">
+        <v>3</v>
+      </c>
+      <c r="M504" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0">
+        <v>7408</v>
+      </c>
+      <c r="B505" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C505" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="D505" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="E505" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F503" s="0">
-        <v>1</v>
-      </c>
-      <c r="G503" s="0">
-        <v>1</v>
-      </c>
-      <c r="H503" s="0">
-        <v>0</v>
-      </c>
-      <c r="I503" s="0">
-        <v>1</v>
-      </c>
-      <c r="J503" s="0">
-        <v>1</v>
-      </c>
-      <c r="K503" s="0">
-        <v>0</v>
-      </c>
-      <c r="L503" s="0">
-        <v>1</v>
-      </c>
-      <c r="M503" s="0">
-        <v>1</v>
+      <c r="F505" s="0">
+        <v>1</v>
+      </c>
+      <c r="G505" s="0">
+        <v>1</v>
+      </c>
+      <c r="H505" s="0">
+        <v>0</v>
+      </c>
+      <c r="I505" s="0">
+        <v>1</v>
+      </c>
+      <c r="J505" s="0">
+        <v>1</v>
+      </c>
+      <c r="K505" s="0">
+        <v>0</v>
+      </c>
+      <c r="L505" s="0">
+        <v>1</v>
+      </c>
+      <c r="M505" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0">
+        <v>7482</v>
+      </c>
+      <c r="B506" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C506" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="D506" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="E506" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="F506" s="0">
+        <v>1</v>
+      </c>
+      <c r="G506" s="0">
+        <v>1</v>
+      </c>
+      <c r="H506" s="0">
+        <v>0</v>
+      </c>
+      <c r="I506" s="0">
+        <v>1</v>
+      </c>
+      <c r="J506" s="0">
+        <v>1</v>
+      </c>
+      <c r="K506" s="0">
+        <v>0</v>
+      </c>
+      <c r="L506" s="0">
+        <v>1</v>
+      </c>
+      <c r="M506" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0">
+        <v>7561</v>
+      </c>
+      <c r="B507" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C507" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="D507" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="E507" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="F507" s="0">
+        <v>1</v>
+      </c>
+      <c r="G507" s="0">
+        <v>1</v>
+      </c>
+      <c r="H507" s="0">
+        <v>0</v>
+      </c>
+      <c r="I507" s="0">
+        <v>1</v>
+      </c>
+      <c r="J507" s="0">
+        <v>1</v>
+      </c>
+      <c r="K507" s="0">
+        <v>0</v>
+      </c>
+      <c r="L507" s="0">
+        <v>3</v>
+      </c>
+      <c r="M507" s="0">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -26222,7 +26398,7 @@
         <v>132</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F30" s="0">
         <v>8</v>
@@ -32368,7 +32544,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:M177"/>
+  <dimension ref="A1:M179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -38432,60 +38608,60 @@
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>6225</v>
+        <v>6618</v>
       </c>
       <c r="B149" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>441</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F149" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G149" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H149" s="0">
         <v>0</v>
       </c>
       <c r="I149" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J149" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K149" s="0">
         <v>0</v>
       </c>
       <c r="L149" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M149" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>6815</v>
+        <v>6225</v>
       </c>
       <c r="B150" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="D150" s="0" t="s">
         <v>442</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F150" s="0">
         <v>2</v>
@@ -38506,27 +38682,27 @@
         <v>0</v>
       </c>
       <c r="L150" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M150" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>6903</v>
+        <v>6815</v>
       </c>
       <c r="B151" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="D151" s="0" t="s">
         <v>443</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F151" s="0">
         <v>2</v>
@@ -38547,21 +38723,21 @@
         <v>0</v>
       </c>
       <c r="L151" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M151" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>6917</v>
+        <v>6903</v>
       </c>
       <c r="B152" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D152" s="0" t="s">
         <v>444</v>
@@ -38588,27 +38764,27 @@
         <v>0</v>
       </c>
       <c r="L152" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M152" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>6980</v>
+        <v>6917</v>
       </c>
       <c r="B153" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="D153" s="0" t="s">
         <v>445</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F153" s="0">
         <v>2</v>
@@ -38629,27 +38805,27 @@
         <v>0</v>
       </c>
       <c r="L153" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M153" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>5457</v>
+        <v>6980</v>
       </c>
       <c r="B154" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="D154" s="0" t="s">
         <v>446</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F154" s="0">
         <v>2</v>
@@ -38670,7 +38846,7 @@
         <v>0</v>
       </c>
       <c r="L154" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M154" s="0">
         <v>5</v>
@@ -38678,19 +38854,19 @@
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>5295</v>
+        <v>5457</v>
       </c>
       <c r="B155" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C155" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="D155" s="0" t="s">
         <v>447</v>
       </c>
-      <c r="D155" s="0" t="s">
-        <v>448</v>
-      </c>
       <c r="E155" s="0" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F155" s="0">
         <v>2</v>
@@ -38711,27 +38887,27 @@
         <v>0</v>
       </c>
       <c r="L155" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M155" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>5880</v>
+        <v>5295</v>
       </c>
       <c r="B156" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>98</v>
+        <v>448</v>
       </c>
       <c r="D156" s="0" t="s">
         <v>449</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F156" s="0">
         <v>2</v>
@@ -38760,19 +38936,19 @@
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>7138</v>
+        <v>5880</v>
       </c>
       <c r="B157" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>291</v>
+        <v>98</v>
       </c>
       <c r="D157" s="0" t="s">
         <v>450</v>
       </c>
       <c r="E157" s="0" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F157" s="0">
         <v>2</v>
@@ -38793,7 +38969,7 @@
         <v>0</v>
       </c>
       <c r="L157" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M157" s="0">
         <v>6</v>
@@ -38801,7 +38977,7 @@
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>6219</v>
+        <v>7138</v>
       </c>
       <c r="B158" s="0" t="s">
         <v>286</v>
@@ -38813,7 +38989,7 @@
         <v>451</v>
       </c>
       <c r="E158" s="0" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F158" s="0">
         <v>2</v>
@@ -38837,12 +39013,12 @@
         <v>5</v>
       </c>
       <c r="M158" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>6246</v>
+        <v>6219</v>
       </c>
       <c r="B159" s="0" t="s">
         <v>286</v>
@@ -38883,19 +39059,19 @@
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>7418</v>
+        <v>6246</v>
       </c>
       <c r="B160" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D160" s="0" t="s">
         <v>453</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F160" s="0">
         <v>2</v>
@@ -38916,27 +39092,27 @@
         <v>0</v>
       </c>
       <c r="L160" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M160" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>526</v>
+        <v>7418</v>
       </c>
       <c r="B161" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="D161" s="0" t="s">
         <v>454</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F161" s="0">
         <v>2</v>
@@ -38957,68 +39133,68 @@
         <v>0</v>
       </c>
       <c r="L161" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M161" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>7165</v>
+        <v>526</v>
       </c>
       <c r="B162" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D162" s="0" t="s">
         <v>455</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F162" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G162" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" s="0">
         <v>0</v>
       </c>
       <c r="I162" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J162" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K162" s="0">
         <v>0</v>
       </c>
       <c r="L162" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M162" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>7357</v>
+        <v>7165</v>
       </c>
       <c r="B163" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D163" s="0" t="s">
         <v>456</v>
       </c>
       <c r="E163" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F163" s="0">
         <v>1</v>
@@ -39047,19 +39223,19 @@
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>7456</v>
+        <v>7357</v>
       </c>
       <c r="B164" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D164" s="0" t="s">
         <v>457</v>
       </c>
       <c r="E164" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F164" s="0">
         <v>1</v>
@@ -39080,21 +39256,21 @@
         <v>0</v>
       </c>
       <c r="L164" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M164" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>5725</v>
+        <v>7456</v>
       </c>
       <c r="B165" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>458</v>
@@ -39129,19 +39305,19 @@
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>6191</v>
+        <v>5725</v>
       </c>
       <c r="B166" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D166" s="0" t="s">
         <v>459</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F166" s="0">
         <v>1</v>
@@ -39162,21 +39338,21 @@
         <v>0</v>
       </c>
       <c r="L166" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M166" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>7345</v>
+        <v>6191</v>
       </c>
       <c r="B167" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D167" s="0" t="s">
         <v>460</v>
@@ -39211,19 +39387,19 @@
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>7248</v>
+        <v>7345</v>
       </c>
       <c r="B168" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="D168" s="0" t="s">
         <v>461</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F168" s="0">
         <v>1</v>
@@ -39244,15 +39420,15 @@
         <v>0</v>
       </c>
       <c r="L168" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M168" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>6410</v>
+        <v>7248</v>
       </c>
       <c r="B169" s="0" t="s">
         <v>286</v>
@@ -39285,15 +39461,15 @@
         <v>0</v>
       </c>
       <c r="L169" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M169" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>7319</v>
+        <v>6410</v>
       </c>
       <c r="B170" s="0" t="s">
         <v>286</v>
@@ -39326,27 +39502,27 @@
         <v>0</v>
       </c>
       <c r="L170" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M170" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>7276</v>
+        <v>7319</v>
       </c>
       <c r="B171" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>341</v>
+        <v>291</v>
       </c>
       <c r="D171" s="0" t="s">
         <v>464</v>
       </c>
       <c r="E171" s="0" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F171" s="0">
         <v>1</v>
@@ -39367,27 +39543,27 @@
         <v>0</v>
       </c>
       <c r="L171" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M171" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>7157</v>
+        <v>7276</v>
       </c>
       <c r="B172" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>291</v>
+        <v>341</v>
       </c>
       <c r="D172" s="0" t="s">
         <v>465</v>
       </c>
       <c r="E172" s="0" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F172" s="0">
         <v>1</v>
@@ -39408,27 +39584,27 @@
         <v>0</v>
       </c>
       <c r="L172" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M172" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>5007</v>
+        <v>7157</v>
       </c>
       <c r="B173" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D173" s="0" t="s">
         <v>466</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="F173" s="0">
         <v>1</v>
@@ -39449,21 +39625,21 @@
         <v>0</v>
       </c>
       <c r="L173" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M173" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>6889</v>
+        <v>5007</v>
       </c>
       <c r="B174" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D174" s="0" t="s">
         <v>467</v>
@@ -39498,19 +39674,19 @@
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>7392</v>
+        <v>6889</v>
       </c>
       <c r="B175" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D175" s="0" t="s">
         <v>468</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F175" s="0">
         <v>1</v>
@@ -39531,15 +39707,15 @@
         <v>0</v>
       </c>
       <c r="L175" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M175" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>6212</v>
+        <v>7392</v>
       </c>
       <c r="B176" s="0" t="s">
         <v>286</v>
@@ -39572,50 +39748,132 @@
         <v>0</v>
       </c>
       <c r="L176" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M176" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>7481</v>
+        <v>6212</v>
       </c>
       <c r="B177" s="0" t="s">
         <v>286</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D177" s="0" t="s">
         <v>470</v>
       </c>
       <c r="E177" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F177" s="0">
+        <v>1</v>
+      </c>
+      <c r="G177" s="0">
+        <v>1</v>
+      </c>
+      <c r="H177" s="0">
+        <v>0</v>
+      </c>
+      <c r="I177" s="0">
+        <v>1</v>
+      </c>
+      <c r="J177" s="0">
+        <v>1</v>
+      </c>
+      <c r="K177" s="0">
+        <v>0</v>
+      </c>
+      <c r="L177" s="0">
+        <v>4</v>
+      </c>
+      <c r="M177" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0">
+        <v>7481</v>
+      </c>
+      <c r="B178" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C178" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="D178" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="E178" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="F177" s="0">
-        <v>1</v>
-      </c>
-      <c r="G177" s="0">
-        <v>1</v>
-      </c>
-      <c r="H177" s="0">
-        <v>0</v>
-      </c>
-      <c r="I177" s="0">
-        <v>1</v>
-      </c>
-      <c r="J177" s="0">
-        <v>1</v>
-      </c>
-      <c r="K177" s="0">
-        <v>0</v>
-      </c>
-      <c r="L177" s="0">
-        <v>1</v>
-      </c>
-      <c r="M177" s="0">
+      <c r="F178" s="0">
+        <v>1</v>
+      </c>
+      <c r="G178" s="0">
+        <v>1</v>
+      </c>
+      <c r="H178" s="0">
+        <v>0</v>
+      </c>
+      <c r="I178" s="0">
+        <v>1</v>
+      </c>
+      <c r="J178" s="0">
+        <v>1</v>
+      </c>
+      <c r="K178" s="0">
+        <v>0</v>
+      </c>
+      <c r="L178" s="0">
+        <v>1</v>
+      </c>
+      <c r="M178" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0">
+        <v>6592</v>
+      </c>
+      <c r="B179" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C179" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="D179" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="E179" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="F179" s="0">
+        <v>1</v>
+      </c>
+      <c r="G179" s="0">
+        <v>1</v>
+      </c>
+      <c r="H179" s="0">
+        <v>0</v>
+      </c>
+      <c r="I179" s="0">
+        <v>1</v>
+      </c>
+      <c r="J179" s="0">
+        <v>1</v>
+      </c>
+      <c r="K179" s="0">
+        <v>0</v>
+      </c>
+      <c r="L179" s="0">
+        <v>1</v>
+      </c>
+      <c r="M179" s="0">
         <v>1</v>
       </c>
     </row>
@@ -39629,7 +39887,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -39710,13 +39968,13 @@
         <v>2764</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>19</v>
@@ -39751,13 +40009,13 @@
         <v>5585</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>17</v>
@@ -39792,13 +40050,13 @@
         <v>4871</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>19</v>
@@ -39833,13 +40091,13 @@
         <v>6052</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>29</v>
@@ -39874,13 +40132,13 @@
         <v>6397</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>25</v>
@@ -39915,13 +40173,13 @@
         <v>5951</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>35</v>
@@ -39956,13 +40214,13 @@
         <v>2097</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>27</v>
@@ -39997,13 +40255,13 @@
         <v>6434</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>35</v>
@@ -40038,13 +40296,13 @@
         <v>7017</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>23</v>
@@ -40079,13 +40337,13 @@
         <v>2137</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>21</v>
@@ -40120,13 +40378,13 @@
         <v>5637</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>39</v>
@@ -40161,13 +40419,13 @@
         <v>6435</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>21</v>
@@ -40202,13 +40460,13 @@
         <v>4510</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>25</v>
@@ -40243,13 +40501,13 @@
         <v>531</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>48</v>
@@ -40284,13 +40542,13 @@
         <v>5995</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>21</v>
@@ -40325,13 +40583,13 @@
         <v>6675</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>31</v>
@@ -40366,13 +40624,13 @@
         <v>7071</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>19</v>
@@ -40407,13 +40665,13 @@
         <v>7023</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>27</v>
@@ -40448,13 +40706,13 @@
         <v>6060</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>48</v>
@@ -40489,13 +40747,13 @@
         <v>2061</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>85</v>
@@ -40530,13 +40788,13 @@
         <v>7351</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>293</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>29</v>
@@ -40571,13 +40829,13 @@
         <v>309</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>17</v>
@@ -40612,13 +40870,13 @@
         <v>6572</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>17</v>
@@ -40653,13 +40911,13 @@
         <v>4371</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>21</v>
@@ -40694,13 +40952,13 @@
         <v>4463</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>33</v>
@@ -40735,13 +40993,13 @@
         <v>4728</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>25</v>
@@ -40776,13 +41034,13 @@
         <v>2038</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>48</v>
@@ -40817,13 +41075,13 @@
         <v>7547</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>33</v>
@@ -40858,13 +41116,13 @@
         <v>5734</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>17</v>
@@ -40899,13 +41157,13 @@
         <v>7484</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>51</v>
@@ -40940,13 +41198,13 @@
         <v>6967</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>293</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>23</v>
@@ -40981,13 +41239,13 @@
         <v>4923</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>41</v>
@@ -41022,13 +41280,13 @@
         <v>6229</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>45</v>
@@ -41063,13 +41321,13 @@
         <v>5672</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>37</v>
@@ -41104,13 +41362,13 @@
         <v>7313</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>37</v>
@@ -41145,13 +41403,13 @@
         <v>7347</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>48</v>
@@ -41186,13 +41444,13 @@
         <v>7554</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>45</v>
@@ -41227,13 +41485,13 @@
         <v>6530</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>293</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>56</v>
@@ -41268,13 +41526,13 @@
         <v>5544</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>35</v>
@@ -41309,13 +41567,13 @@
         <v>5029</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>43</v>
@@ -41350,13 +41608,13 @@
         <v>2155</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>53</v>
@@ -41391,13 +41649,13 @@
         <v>6646</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>85</v>
@@ -41432,13 +41690,13 @@
         <v>6643</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>31</v>
@@ -41473,13 +41731,13 @@
         <v>4359</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>31</v>
@@ -41514,13 +41772,13 @@
         <v>6164</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E47" s="0" t="s">
         <v>41</v>
@@ -41555,13 +41813,13 @@
         <v>6904</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>51</v>
@@ -41596,13 +41854,13 @@
         <v>7449</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>51</v>
@@ -41637,13 +41895,13 @@
         <v>5436</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E50" s="0" t="s">
         <v>56</v>
@@ -41678,13 +41936,13 @@
         <v>6669</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E51" s="0" t="s">
         <v>19</v>
@@ -41719,13 +41977,13 @@
         <v>7252</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E52" s="0" t="s">
         <v>43</v>
@@ -41760,13 +42018,13 @@
         <v>608</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E53" s="0" t="s">
         <v>85</v>
@@ -41801,13 +42059,13 @@
         <v>5918</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E54" s="0" t="s">
         <v>21</v>
@@ -41842,13 +42100,13 @@
         <v>6598</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>33</v>
@@ -41883,13 +42141,13 @@
         <v>2832</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C56" s="0" t="s">
         <v>293</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>35</v>
@@ -41924,13 +42182,13 @@
         <v>6556</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E57" s="0" t="s">
         <v>37</v>
@@ -41965,13 +42223,13 @@
         <v>7008</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E58" s="0" t="s">
         <v>25</v>
@@ -42006,13 +42264,13 @@
         <v>6831</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>293</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E59" s="0" t="s">
         <v>29</v>
@@ -42047,13 +42305,13 @@
         <v>4896</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>287</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E60" s="0" t="s">
         <v>33</v>
@@ -42088,13 +42346,13 @@
         <v>6519</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E61" s="0" t="s">
         <v>25</v>
@@ -42129,13 +42387,13 @@
         <v>5882</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E62" s="0" t="s">
         <v>53</v>
@@ -42170,13 +42428,13 @@
         <v>7213</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E63" s="0" t="s">
         <v>45</v>
@@ -42211,13 +42469,13 @@
         <v>4387</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E64" s="0" t="s">
         <v>51</v>
@@ -42249,57 +42507,57 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>6243</v>
+        <v>2012</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F65" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G65" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H65" s="0">
         <v>0</v>
       </c>
       <c r="I65" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J65" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" s="0">
         <v>0</v>
       </c>
       <c r="L65" s="0">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M65" s="0">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>7374</v>
+        <v>6243</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E66" s="0" t="s">
         <v>33</v>
@@ -42331,19 +42589,19 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>313</v>
+        <v>7374</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F67" s="0">
         <v>4</v>
@@ -42364,27 +42622,27 @@
         <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M67" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>6204</v>
+        <v>313</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F68" s="0">
         <v>4</v>
@@ -42396,36 +42654,36 @@
         <v>0</v>
       </c>
       <c r="I68" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J68" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K68" s="0">
         <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M68" s="0">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>7453</v>
+        <v>6204</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F69" s="0">
         <v>4</v>
@@ -42437,36 +42695,36 @@
         <v>0</v>
       </c>
       <c r="I69" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J69" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K69" s="0">
         <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M69" s="0">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>7162</v>
+        <v>7453</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="F70" s="0">
         <v>4</v>
@@ -42478,36 +42736,36 @@
         <v>0</v>
       </c>
       <c r="I70" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J70" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M70" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>7349</v>
+        <v>7162</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="F71" s="0">
         <v>4</v>
@@ -42519,36 +42777,36 @@
         <v>0</v>
       </c>
       <c r="I71" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" s="0">
         <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M71" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>7272</v>
+        <v>7349</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="F72" s="0">
         <v>4</v>
@@ -42569,27 +42827,27 @@
         <v>0</v>
       </c>
       <c r="L72" s="0">
+        <v>9</v>
+      </c>
+      <c r="M72" s="0">
         <v>7</v>
-      </c>
-      <c r="M72" s="0">
-        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>7546</v>
+        <v>7272</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F73" s="0">
         <v>4</v>
@@ -42601,42 +42859,42 @@
         <v>0</v>
       </c>
       <c r="I73" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M73" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>7128</v>
+        <v>7546</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F74" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74" s="0">
         <v>0</v>
@@ -42651,27 +42909,27 @@
         <v>0</v>
       </c>
       <c r="L74" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M74" s="0">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>6822</v>
+        <v>7128</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>471</v>
+        <v>293</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F75" s="0">
         <v>3</v>
@@ -42683,36 +42941,36 @@
         <v>0</v>
       </c>
       <c r="I75" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M75" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>7001</v>
+        <v>6822</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>293</v>
+        <v>473</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F76" s="0">
         <v>3</v>
@@ -42724,36 +42982,36 @@
         <v>0</v>
       </c>
       <c r="I76" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J76" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76" s="0">
         <v>0</v>
       </c>
       <c r="L76" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M76" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>7523</v>
+        <v>7001</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F77" s="0">
         <v>3</v>
@@ -42765,36 +43023,36 @@
         <v>0</v>
       </c>
       <c r="I77" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J77" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M77" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>7120</v>
+        <v>7523</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F78" s="0">
         <v>3</v>
@@ -42815,24 +43073,24 @@
         <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M78" s="0">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>6215</v>
+        <v>7120</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E79" s="0" t="s">
         <v>29</v>
@@ -42859,24 +43117,24 @@
         <v>10</v>
       </c>
       <c r="M79" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>7342</v>
+        <v>6215</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F80" s="0">
         <v>3</v>
@@ -42897,68 +43155,68 @@
         <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M80" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>383</v>
+        <v>7342</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F81" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="0">
         <v>0</v>
       </c>
       <c r="I81" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J81" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" s="0">
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M81" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>7249</v>
+        <v>383</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F82" s="0">
         <v>2</v>
@@ -42979,65 +43237,65 @@
         <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M82" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>7338</v>
+        <v>7249</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F83" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83" s="0">
         <v>0</v>
       </c>
       <c r="I83" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K83" s="0">
         <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M83" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>7317</v>
+        <v>7338</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E84" s="0" t="s">
         <v>33</v>
@@ -43061,27 +43319,27 @@
         <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M84" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>7027</v>
+        <v>7317</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F85" s="0">
         <v>1</v>
@@ -43102,27 +43360,27 @@
         <v>0</v>
       </c>
       <c r="L85" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>6981</v>
+        <v>7027</v>
       </c>
       <c r="B86" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F86" s="0">
         <v>1</v>
@@ -43143,27 +43401,27 @@
         <v>0</v>
       </c>
       <c r="L86" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M86" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>7158</v>
+        <v>6981</v>
       </c>
       <c r="B87" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F87" s="0">
         <v>1</v>
@@ -43184,27 +43442,27 @@
         <v>0</v>
       </c>
       <c r="L87" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M87" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>7161</v>
+        <v>7158</v>
       </c>
       <c r="B88" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F88" s="0">
         <v>1</v>
@@ -43225,27 +43483,27 @@
         <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M88" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>7408</v>
+        <v>7161</v>
       </c>
       <c r="B89" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>293</v>
+        <v>474</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F89" s="0">
         <v>1</v>
@@ -43266,24 +43524,24 @@
         <v>0</v>
       </c>
       <c r="L89" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M89" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>7482</v>
+        <v>7408</v>
       </c>
       <c r="B90" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>472</v>
+        <v>293</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E90" s="0" t="s">
         <v>51</v>
@@ -43311,6 +43569,88 @@
       </c>
       <c r="M90" s="0">
         <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0">
+        <v>7482</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>474</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="F91" s="0">
+        <v>1</v>
+      </c>
+      <c r="G91" s="0">
+        <v>1</v>
+      </c>
+      <c r="H91" s="0">
+        <v>0</v>
+      </c>
+      <c r="I91" s="0">
+        <v>1</v>
+      </c>
+      <c r="J91" s="0">
+        <v>1</v>
+      </c>
+      <c r="K91" s="0">
+        <v>0</v>
+      </c>
+      <c r="L91" s="0">
+        <v>1</v>
+      </c>
+      <c r="M91" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0">
+        <v>7561</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C92" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="F92" s="0">
+        <v>1</v>
+      </c>
+      <c r="G92" s="0">
+        <v>1</v>
+      </c>
+      <c r="H92" s="0">
+        <v>0</v>
+      </c>
+      <c r="I92" s="0">
+        <v>1</v>
+      </c>
+      <c r="J92" s="0">
+        <v>1</v>
+      </c>
+      <c r="K92" s="0">
+        <v>0</v>
+      </c>
+      <c r="L92" s="0">
+        <v>3</v>
+      </c>
+      <c r="M92" s="0">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -43343,7 +43683,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -43410,7 +43750,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>21</v>
@@ -43451,7 +43791,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>33</v>
@@ -43492,7 +43832,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>43</v>
@@ -43533,7 +43873,7 @@
         <v>15</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>43</v>
@@ -43574,7 +43914,7 @@
         <v>133</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>29</v>
@@ -43615,7 +43955,7 @@
         <v>103</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>21</v>
@@ -43656,7 +43996,7 @@
         <v>116</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>25</v>
@@ -43697,7 +44037,7 @@
         <v>100</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>17</v>
@@ -43738,7 +44078,7 @@
         <v>116</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>33</v>
@@ -43779,7 +44119,7 @@
         <v>110</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>41</v>
@@ -43820,7 +44160,7 @@
         <v>110</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>43</v>
@@ -43861,7 +44201,7 @@
         <v>293</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>45</v>
@@ -43902,7 +44242,7 @@
         <v>98</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>51</v>
@@ -43937,13 +44277,13 @@
         <v>2531</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>29</v>
